--- a/client-course-schedulizer/csv/test_mutiple/1_test.xlsx
+++ b/client-course-schedulizer/csv/test_mutiple/1_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\李约瑟\Desktop\sen\course-schedulizer\client-course-schedulizer\csv\test_mutiple\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E8935EC-4CFC-4F9B-93E9-24EEBAE94CBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DF1903D-6624-4FB8-AA17-15BBE7C578BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="39912" windowHeight="16584" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Schedulizer Course Sections" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="111">
   <si>
     <t>Department</t>
   </si>
@@ -109,9 +109,6 @@
     <t>A</t>
   </si>
   <si>
-    <t>Erek Kooyman</t>
-  </si>
-  <si>
     <t>MW</t>
   </si>
   <si>
@@ -149,9 +146,6 @@
   </si>
   <si>
     <t>B</t>
-  </si>
-  <si>
-    <t>Jenny Griffin</t>
   </si>
   <si>
     <t>MWF
@@ -188,9 +182,6 @@
     <t>04</t>
   </si>
   <si>
-    <t>Stacy DeRuiter</t>
-  </si>
-  <si>
     <t>MWF</t>
   </si>
   <si>
@@ -200,15 +191,9 @@
     <t>65</t>
   </si>
   <si>
-    <t>HH 331</t>
-  </si>
-  <si>
     <t>Community and Commitments</t>
   </si>
   <si>
-    <t>James Turner</t>
-  </si>
-  <si>
     <t>12:15:00</t>
   </si>
   <si>
@@ -227,18 +212,12 @@
     <t>171</t>
   </si>
   <si>
-    <t>Mike Bolt</t>
-  </si>
-  <si>
     <t>08:00:00</t>
   </si>
   <si>
     <t>Calculus I</t>
   </si>
   <si>
-    <t>Timothy Pennings</t>
-  </si>
-  <si>
     <t>14:45:00</t>
   </si>
   <si>
@@ -257,12 +236,6 @@
     <t>13:30:00</t>
   </si>
   <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>John Ferdinands</t>
-  </si>
-  <si>
     <t>NH 253</t>
   </si>
   <si>
@@ -275,9 +248,6 @@
     <t>190</t>
   </si>
   <si>
-    <t>John Ferdinands, Thomas Scofield</t>
-  </si>
-  <si>
     <t>W</t>
   </si>
   <si>
@@ -293,9 +263,6 @@
     <t>221</t>
   </si>
   <si>
-    <t>Dave Klanderman</t>
-  </si>
-  <si>
     <t>NH 251</t>
   </si>
   <si>
@@ -305,11 +272,119 @@
     <t>200</t>
   </si>
   <si>
-    <t>AY25</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mathematics and Statistics</t>
+    <t>MATH</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>one</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>two</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>three</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>four</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>five</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>six</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>seven</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>eight</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>nine</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>ten</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>twlvlv</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>thirten</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>furten</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>fiften</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>evelyn</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>first</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Online</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>cats</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>HH 333</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MF</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>G</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>CS</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Half</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SP</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Lord forgive me </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>12 is being a baaad section</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>I wish im as smart as professor arnold</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>CourseNumber Section and Prefix  CourseNumber modified problems</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -398,7 +473,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
@@ -407,6 +482,9 @@
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="21" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -878,11 +956,11 @@
       </c>
     </row>
     <row r="2" spans="1:22" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>93</v>
+      <c r="A2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>24</v>
@@ -890,8 +968,8 @@
       <c r="D2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>26</v>
+      <c r="E2" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>27</v>
@@ -899,8 +977,8 @@
       <c r="G2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>29</v>
+      <c r="H2" s="3" t="s">
+        <v>83</v>
       </c>
       <c r="I2" s="2">
         <v>4</v>
@@ -910,31 +988,31 @@
       </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="R2" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="S2" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>98</v>
       </c>
       <c r="U2" s="2">
         <v>15</v>
@@ -945,28 +1023,28 @@
     </row>
     <row r="3" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>43</v>
+      <c r="H3" s="3" t="s">
+        <v>84</v>
       </c>
       <c r="I3" s="2">
         <v>2</v>
@@ -976,31 +1054,29 @@
       </c>
       <c r="K3" s="2"/>
       <c r="L3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="O3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="P3" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="O3" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>37</v>
+      <c r="Q3" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="R3" s="2">
+        <v>100</v>
+      </c>
+      <c r="S3" s="2"/>
+      <c r="T3" s="3" t="s">
+        <v>107</v>
       </c>
       <c r="U3" s="2">
         <v>20</v>
@@ -1011,7 +1087,7 @@
     </row>
     <row r="4" spans="1:22" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>23</v>
@@ -1023,16 +1099,16 @@
         <v>25</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>43</v>
+      <c r="H4" s="3" t="s">
+        <v>85</v>
       </c>
       <c r="I4" s="2">
         <v>2</v>
@@ -1042,31 +1118,31 @@
       </c>
       <c r="K4" s="2"/>
       <c r="L4" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="N4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="N4" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="O4" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="P4" s="2" t="s">
         <v>48</v>
       </c>
+      <c r="P4" s="3" t="s">
+        <v>100</v>
+      </c>
       <c r="Q4" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U4" s="2">
         <v>13</v>
@@ -1077,28 +1153,28 @@
     </row>
     <row r="5" spans="1:22" ht="15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>86</v>
       </c>
       <c r="I5" s="2">
         <v>2</v>
@@ -1108,31 +1184,31 @@
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="P5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M5" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>59</v>
-      </c>
       <c r="Q5" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U5" s="2">
         <v>23</v>
@@ -1149,7 +1225,7 @@
         <v>23</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>25</v>
@@ -1158,13 +1234,13 @@
         <v>26</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>60</v>
+      <c r="H6" s="3" t="s">
+        <v>87</v>
       </c>
       <c r="I6" s="2">
         <v>4</v>
@@ -1174,31 +1250,31 @@
       </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>32</v>
+        <v>56</v>
+      </c>
+      <c r="N6" s="2">
+        <v>101</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U6" s="2">
         <v>9</v>
@@ -1215,7 +1291,7 @@
         <v>23</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>25</v>
@@ -1224,13 +1300,13 @@
         <v>26</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>43</v>
+      <c r="H7" s="3" t="s">
+        <v>88</v>
       </c>
       <c r="I7" s="2">
         <v>2</v>
@@ -1240,31 +1316,31 @@
       </c>
       <c r="K7" s="2"/>
       <c r="L7" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>61</v>
+        <v>52</v>
+      </c>
+      <c r="M7" s="4">
+        <v>0.50902777777777775</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U7" s="2">
         <v>17</v>
@@ -1281,7 +1357,7 @@
         <v>23</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>25</v>
@@ -1290,13 +1366,13 @@
         <v>26</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>67</v>
+      <c r="H8" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="I8" s="2">
         <v>4</v>
@@ -1305,32 +1381,32 @@
         <v>4</v>
       </c>
       <c r="K8" s="2"/>
-      <c r="L8" s="2" t="s">
-        <v>55</v>
+      <c r="L8" s="3" t="s">
+        <v>102</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U8" s="2">
         <v>27</v>
@@ -1347,7 +1423,7 @@
         <v>23</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>25</v>
@@ -1356,47 +1432,47 @@
         <v>26</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>70</v>
+        <v>41</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>90</v>
       </c>
       <c r="I9" s="2">
         <v>4</v>
       </c>
       <c r="J9" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K9" s="2"/>
       <c r="L9" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U9" s="2">
         <v>21</v>
@@ -1413,7 +1489,7 @@
         <v>23</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>25</v>
@@ -1422,47 +1498,47 @@
         <v>26</v>
       </c>
       <c r="F10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>67</v>
+      <c r="H10" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="I10" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J10" s="2">
         <v>4</v>
       </c>
       <c r="K10" s="2"/>
       <c r="L10" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U10" s="2">
         <v>25</v>
@@ -1479,7 +1555,7 @@
         <v>23</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>25</v>
@@ -1488,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="I11" s="2">
         <v>4</v>
@@ -1504,31 +1580,31 @@
       </c>
       <c r="K11" s="2"/>
       <c r="L11" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U11" s="2">
         <v>24</v>
@@ -1545,7 +1621,7 @@
         <v>23</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>25</v>
@@ -1554,13 +1630,13 @@
         <v>26</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>78</v>
+        <v>61</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>97</v>
       </c>
       <c r="I12" s="2">
         <v>4</v>
@@ -1570,31 +1646,31 @@
       </c>
       <c r="K12" s="2"/>
       <c r="L12" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U12" s="2">
         <v>27</v>
@@ -1603,7 +1679,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:22" ht="15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>22</v>
       </c>
@@ -1611,7 +1687,7 @@
         <v>23</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>25</v>
@@ -1619,14 +1695,14 @@
       <c r="E13" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>80</v>
+      <c r="F13" s="2">
+        <v>175</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H13" s="2" t="s">
-        <v>78</v>
+      <c r="H13" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="I13" s="2">
         <v>4</v>
@@ -1636,31 +1712,31 @@
       </c>
       <c r="K13" s="2"/>
       <c r="L13" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="T13" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
+      </c>
+      <c r="T13" s="3" t="s">
+        <v>108</v>
       </c>
       <c r="U13" s="2">
         <v>32</v>
@@ -1669,7 +1745,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:22" ht="15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>22</v>
       </c>
@@ -1677,22 +1753,22 @@
         <v>23</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>26</v>
+      <c r="E14" s="3" t="s">
+        <v>104</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>78</v>
+        <v>41</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="I14" s="2">
         <v>4</v>
@@ -1702,31 +1778,31 @@
       </c>
       <c r="K14" s="2"/>
       <c r="L14" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="T14" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>109</v>
       </c>
       <c r="U14" s="2">
         <v>27</v>
@@ -1743,22 +1819,22 @@
         <v>23</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>25</v>
+        <v>38</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H15" s="2" t="s">
-        <v>83</v>
+      <c r="H15" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="I15" s="2">
         <v>0</v>
@@ -1768,31 +1844,31 @@
       </c>
       <c r="K15" s="2"/>
       <c r="L15" s="2" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U15" s="2">
         <v>2</v>
@@ -1801,15 +1877,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>39</v>
+      <c r="C16" s="3" t="s">
+        <v>106</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>25</v>
@@ -1818,13 +1894,13 @@
         <v>26</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H16" s="2" t="s">
-        <v>89</v>
+      <c r="H16" s="3" t="s">
+        <v>96</v>
       </c>
       <c r="I16" s="2">
         <v>4</v>
@@ -1834,31 +1910,31 @@
       </c>
       <c r="K16" s="2"/>
       <c r="L16" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="T16" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
+      </c>
+      <c r="T16" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="U16" s="2">
         <v>30</v>
